--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\fs_test2\src\test\resources\dataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84E8A989-E62F-4139-BF98-F8632EED30A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B7B192-16D0-44E0-8567-87B126343F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="864" windowWidth="17280" windowHeight="8976" xr2:uid="{4A8A3549-3177-431C-B066-9275D516E229}"/>
+    <workbookView xWindow="4464" yWindow="2928" windowWidth="17280" windowHeight="8976" xr2:uid="{4A8A3549-3177-431C-B066-9275D516E229}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,18 +33,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>r1c1</t>
-  </si>
-  <si>
-    <t>r1c2</t>
-  </si>
-  <si>
-    <t>r2c1</t>
-  </si>
-  <si>
-    <t>r2c2</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>row2cell0</t>
+  </si>
+  <si>
+    <t>row2cell1</t>
+  </si>
+  <si>
+    <t>row1cell2</t>
+  </si>
+  <si>
+    <t>row1cell3</t>
+  </si>
+  <si>
+    <t>row1cell4</t>
+  </si>
+  <si>
+    <t>row1cell5</t>
+  </si>
+  <si>
+    <t>row0cell0</t>
+  </si>
+  <si>
+    <t>row0cell1</t>
+  </si>
+  <si>
+    <t>row0cell2</t>
+  </si>
+  <si>
+    <t>row0cell3</t>
+  </si>
+  <si>
+    <t>row0cell4</t>
+  </si>
+  <si>
+    <t>row0cell5</t>
+  </si>
+  <si>
+    <t>row1cell0</t>
+  </si>
+  <si>
+    <t>row1cell1</t>
+  </si>
+  <si>
+    <t>row2cell2</t>
+  </si>
+  <si>
+    <t>row2cell3</t>
+  </si>
+  <si>
+    <t>row2cell4</t>
+  </si>
+  <si>
+    <t>row2cell5</t>
+  </si>
+  <si>
+    <t>row3cell0</t>
+  </si>
+  <si>
+    <t>row3cell1</t>
+  </si>
+  <si>
+    <t>row3cell2</t>
+  </si>
+  <si>
+    <t>row3cell3</t>
+  </si>
+  <si>
+    <t>row3cell4</t>
+  </si>
+  <si>
+    <t>row3cell5</t>
   </si>
 </sst>
 </file>
@@ -396,23 +456,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B6F147-FF26-4BA7-AF32-9A892F4724FA}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,9 +12,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
-    <t>?TSI=Test21</t>
+    <t>?TSI=Test38</t>
+  </si>
+  <si>
+    <t>?TSI=Test94</t>
+  </si>
+  <si>
+    <t>?TSI=Test17</t>
+  </si>
+  <si>
+    <t>?TSI=Test7</t>
+  </si>
+  <si>
+    <t>?TSI=Test32</t>
+  </si>
+  <si>
+    <t>?TSI=Test67</t>
+  </si>
+  <si>
+    <t>?TSI=Test3</t>
+  </si>
+  <si>
+    <t>?TSI=Test76</t>
   </si>
 </sst>
 </file>
@@ -59,12 +80,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="C3"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="3">
-      <c r="C3" t="s">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -1,51 +1,85 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\fs_test2\src\test\resources\dataFile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836C3D49-7B50-4162-B674-AE134CF37D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="5436" yWindow="1104" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FIRST SHEET" r:id="rId3" sheetId="1"/>
+    <sheet name="FIRST SHEET" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
-  <si>
-    <t>?TSI=Test38</t>
-  </si>
-  <si>
-    <t>?TSI=Test94</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+  <si>
+    <t>?TSI=Test58</t>
+  </si>
+  <si>
+    <t>?TSI=Test47</t>
+  </si>
+  <si>
+    <t>?TSI=Test62</t>
+  </si>
+  <si>
+    <t>?TSI=Test91</t>
+  </si>
+  <si>
+    <t>?TSI=Test66</t>
+  </si>
+  <si>
+    <t>?TSI=Test73</t>
+  </si>
+  <si>
+    <t>?TSI=Test6</t>
   </si>
   <si>
     <t>?TSI=Test17</t>
   </si>
   <si>
-    <t>?TSI=Test7</t>
+    <t>?TSI=Test86</t>
+  </si>
+  <si>
+    <t>?TSI=Test85</t>
+  </si>
+  <si>
+    <t>?TSI=Test98</t>
+  </si>
+  <si>
+    <t>?TSI=Test71</t>
+  </si>
+  <si>
+    <t>?TSI=Test57</t>
+  </si>
+  <si>
+    <t>?TSI=Test26</t>
+  </si>
+  <si>
+    <t>?TSI=Test21</t>
+  </si>
+  <si>
+    <t>?TSI=Test64</t>
   </si>
   <si>
     <t>?TSI=Test32</t>
-  </si>
-  <si>
-    <t>?TSI=Test67</t>
-  </si>
-  <si>
-    <t>?TSI=Test3</t>
-  </si>
-  <si>
-    <t>?TSI=Test76</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,7 +91,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -75,65 +109,426 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\fs_test2\src\test\resources\dataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836C3D49-7B50-4162-B674-AE134CF37D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4857DBE3-E886-41B3-AD83-BC8AE506E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5436" yWindow="1104" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2892" yWindow="288" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIRST SHEET" sheetId="1" r:id="rId1"/>
@@ -20,57 +20,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+  <si>
+    <t>?TSI=Test71</t>
+  </si>
+  <si>
+    <t>?TSI=Test37</t>
+  </si>
+  <si>
+    <t>?TSI=Test33</t>
+  </si>
+  <si>
+    <t>?TSI=Test35</t>
+  </si>
+  <si>
+    <t>?TSI=Test48</t>
+  </si>
+  <si>
+    <t>?TSI=Test39</t>
+  </si>
+  <si>
+    <t>?TSI=Test22</t>
+  </si>
+  <si>
+    <t>?TSI=Test49</t>
+  </si>
+  <si>
+    <t>?TSI=Test10</t>
+  </si>
+  <si>
+    <t>?TSI=Test23</t>
+  </si>
+  <si>
+    <t>?TSI=Test40</t>
+  </si>
   <si>
     <t>?TSI=Test58</t>
   </si>
   <si>
+    <t>?TSI=Test5</t>
+  </si>
+  <si>
+    <t>?TSI=Test78</t>
+  </si>
+  <si>
+    <t>?TSI=Test54</t>
+  </si>
+  <si>
+    <t>?TSI=Test91</t>
+  </si>
+  <si>
+    <t>?TSI=Test88</t>
+  </si>
+  <si>
+    <t>?TSI=Test87</t>
+  </si>
+  <si>
+    <t>?TSI=Test69</t>
+  </si>
+  <si>
+    <t>?TSI=Test42</t>
+  </si>
+  <si>
+    <t>?TSI=Test17</t>
+  </si>
+  <si>
+    <t>?TSI=Test41</t>
+  </si>
+  <si>
     <t>?TSI=Test47</t>
   </si>
   <si>
-    <t>?TSI=Test62</t>
-  </si>
-  <si>
-    <t>?TSI=Test91</t>
-  </si>
-  <si>
-    <t>?TSI=Test66</t>
-  </si>
-  <si>
-    <t>?TSI=Test73</t>
-  </si>
-  <si>
-    <t>?TSI=Test6</t>
-  </si>
-  <si>
-    <t>?TSI=Test17</t>
-  </si>
-  <si>
-    <t>?TSI=Test86</t>
-  </si>
-  <si>
-    <t>?TSI=Test85</t>
-  </si>
-  <si>
-    <t>?TSI=Test98</t>
-  </si>
-  <si>
-    <t>?TSI=Test71</t>
-  </si>
-  <si>
-    <t>?TSI=Test57</t>
-  </si>
-  <si>
-    <t>?TSI=Test26</t>
-  </si>
-  <si>
-    <t>?TSI=Test21</t>
-  </si>
-  <si>
-    <t>?TSI=Test64</t>
-  </si>
-  <si>
-    <t>?TSI=Test32</t>
+    <t>?TSI=Test28</t>
+  </si>
+  <si>
+    <t>?TSI=Test83</t>
   </si>
 </sst>
 </file>
@@ -422,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -450,62 +474,62 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
@@ -515,17 +539,67 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\fs_test2\src\test\resources\dataFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4857DBE3-E886-41B3-AD83-BC8AE506E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7122AAE-D6AC-4802-B773-26F3E84B74E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="288" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2892" yWindow="288" windowWidth="17280" windowHeight="7464" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FIRST SHEET" sheetId="1" r:id="rId1"/>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,109 +14,109 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
-    <t>?TSI=Test20850e25-3bd5-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test6e01b853-6ab4-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test2f712138-76a5-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testfb66c2f0-8472-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test358c25de-66ba-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testdfc9053c-5d8e-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test4581508d-bd4c-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testfa0c2ab8-c8ad-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test926fce9d-fb3b-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test28fe5102-9380-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test00a16653-83e4-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test009dadde-b75c-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test1927b779-5130-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testc0c7e3bb-bae5-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test5bd316de-7d3c-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test0b3992cf-6de7-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test50b77a66-d0fd-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test0f98b5b1-0942-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test52829e94-5685-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testd7cc51fe-1cdc-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test94e02fb9-34d6-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test36c2178b-0a61-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test80dd28e0-2b4b-4</t>
-  </si>
-  <si>
-    <t>?TSI=Teste22e3270-ca3a-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test6e00a99c-b980-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testeec656eb-e8ca-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testd2ba29b2-f2cc-4</t>
-  </si>
-  <si>
-    <t>?TSI=Teste13c45e5-a367-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test8a47396c-1052-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testf0f76ef1-f135-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test381fd374-e053-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testdb85b603-6f10-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testf37a8e20-a510-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test416ee580-2174-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testdb88ba1a-212f-4</t>
+    <t>?TSI=Testeba9882d-3ac4-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test494f55b7-f08a-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test34fa3d01-bfb9-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test3303f17e-b4fd-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testa6ddc5e8-c17d-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test23afb627-2ec5-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testa840a439-422d-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test561b5734-c6a8-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test29979e55-0b1b-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test84f653af-dbfb-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test48d73add-5345-4</t>
+  </si>
+  <si>
+    <t>?TSI=Teste2b8b27e-1e1f-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test28c1453d-8f50-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test4044cef2-9601-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test7e6cd901-333e-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test5ae9ea99-4020-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test2ca8ea80-9466-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test40f3d936-5a26-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test69920b3a-0d24-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testf40567a9-d6a1-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test8bdd40f7-0fb9-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test6e79a63b-8ee5-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testc33c09cd-1379-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testbe388dbd-bcd8-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test8f1af7a7-9e8b-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test6cc8c4ba-7611-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test2946f707-1465-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test72254bc1-5c68-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test58a07934-4cb4-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test2f6a9536-348c-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test1061dd28-693f-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test64e379b9-1d93-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test66e3253a-9e19-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test65bae663-8e09-4</t>
+  </si>
+  <si>
+    <t>?TSI=Testf6c833a7-c5ae-4</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>?TSI=Test5f442739-7</t>
+    <t>?TSI=Test3f0ab083-2</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>?TSI=Test3f0ab083-2</t>
+    <t>?TSI=Testd94a3e73-5</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>?TSI=Testd94a3e73-5</t>
+    <t>?TSI=Testb2b5d676-9</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>?TSI=Testb2b5d676-9</t>
+    <t>?TSI=Test2cb50246-5</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,9 +12,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>?TSI=Test2cb50246-5</t>
+    <t>?TSI=Test04c15037-4</t>
+  </si>
+  <si>
+    <t>?TSI=Test10e779ad-e</t>
+  </si>
+  <si>
+    <t>?TSI=Test6f0a79ef-7</t>
+  </si>
+  <si>
+    <t>?TSI=Test78185f98-3</t>
+  </si>
+  <si>
+    <t>?TSI=Test70d2af1a-6</t>
   </si>
 </sst>
 </file>
@@ -59,7 +71,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -67,6 +79,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,21 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>?TSI=Test04c15037-4</t>
-  </si>
-  <si>
-    <t>?TSI=Test10e779ad-e</t>
-  </si>
-  <si>
-    <t>?TSI=Test6f0a79ef-7</t>
-  </si>
-  <si>
-    <t>?TSI=Test78185f98-3</t>
-  </si>
-  <si>
-    <t>?TSI=Test70d2af1a-6</t>
+    <t>?TSI=Test9260f115-4</t>
   </si>
 </sst>
 </file>
@@ -71,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -79,26 +67,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>?TSI=Test9260f115-4</t>
+    <t>?TSI=Test9b53087c-5</t>
+  </si>
+  <si>
+    <t>?TSI=Testb6009540-1</t>
+  </si>
+  <si>
+    <t>?TSI=Test1e662728-5</t>
   </si>
 </sst>
 </file>
@@ -59,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -67,6 +73,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,15 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Test9b53087c-5</t>
+    <t>?TSI=Test227156fe-6</t>
   </si>
   <si>
-    <t>?TSI=Testb6009540-1</t>
-  </si>
-  <si>
-    <t>?TSI=Test1e662728-5</t>
+    <t>?TSI=Test6b0de9f9-2</t>
   </si>
 </sst>
 </file>
@@ -65,7 +62,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -78,11 +75,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Test227156fe-6</t>
+    <t>?TSI=Test75323e43-9</t>
   </si>
   <si>
-    <t>?TSI=Test6b0de9f9-2</t>
+    <t>?TSI=Test0b8d0229-6</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,12 +12,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>?TSI=Test75323e43-9</t>
+    <t>?TSI=Testd116ee29-6</t>
   </si>
   <si>
-    <t>?TSI=Test0b8d0229-6</t>
+    <t>?TSI=Test60724077-b</t>
+  </si>
+  <si>
+    <t>?TSI=Test2f70ee9f-6</t>
+  </si>
+  <si>
+    <t>?TSI=Testcdd118b0-e</t>
+  </si>
+  <si>
+    <t>?TSI=Test7a2ad517-0</t>
+  </si>
+  <si>
+    <t>?TSI=Testd5b7eb27-7</t>
+  </si>
+  <si>
+    <t>?TSI=Testbb9fb2a2-d</t>
+  </si>
+  <si>
+    <t>?TSI=Testf4046315-b</t>
+  </si>
+  <si>
+    <t>?TSI=Test7995b73f-8</t>
+  </si>
+  <si>
+    <t>?TSI=Test26766ebc-c</t>
   </si>
 </sst>
 </file>
@@ -62,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -75,6 +99,46 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,34 +14,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>?TSI=Testd116ee29-6</t>
+    <t>?TSI=Testb68f96a3-3</t>
   </si>
   <si>
-    <t>?TSI=Test60724077-b</t>
+    <t>?TSI=Test8ea9d883-2</t>
   </si>
   <si>
-    <t>?TSI=Test2f70ee9f-6</t>
+    <t>?TSI=Testafab6d79-c</t>
   </si>
   <si>
-    <t>?TSI=Testcdd118b0-e</t>
+    <t>?TSI=Testedee2e7c-b</t>
   </si>
   <si>
-    <t>?TSI=Test7a2ad517-0</t>
+    <t>?TSI=Testdbb3935d-2</t>
   </si>
   <si>
-    <t>?TSI=Testd5b7eb27-7</t>
+    <t>?TSI=Testbc5216f2-f</t>
   </si>
   <si>
-    <t>?TSI=Testbb9fb2a2-d</t>
+    <t>?TSI=Teste844a963-b</t>
   </si>
   <si>
-    <t>?TSI=Testf4046315-b</t>
+    <t>?TSI=Test03179da7-e</t>
   </si>
   <si>
-    <t>?TSI=Test7995b73f-8</t>
+    <t>?TSI=Test13ead7fe-9</t>
   </si>
   <si>
-    <t>?TSI=Test26766ebc-c</t>
+    <t>?TSI=Test50b9ae3e-8</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,34 +14,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>?TSI=Testb68f96a3-3</t>
+    <t>?TSI=Testb8285b25-2</t>
   </si>
   <si>
-    <t>?TSI=Test8ea9d883-2</t>
+    <t>?TSI=Test3c9125d2-9</t>
   </si>
   <si>
-    <t>?TSI=Testafab6d79-c</t>
+    <t>?TSI=Test0bdc7da3-3</t>
   </si>
   <si>
-    <t>?TSI=Testedee2e7c-b</t>
+    <t>?TSI=Testc9bb09be-2</t>
   </si>
   <si>
-    <t>?TSI=Testdbb3935d-2</t>
+    <t>?TSI=Test55c4bff8-6</t>
   </si>
   <si>
-    <t>?TSI=Testbc5216f2-f</t>
+    <t>?TSI=Test8049fc90-1</t>
   </si>
   <si>
-    <t>?TSI=Teste844a963-b</t>
+    <t>?TSI=Testd48f5f9d-a</t>
   </si>
   <si>
-    <t>?TSI=Test03179da7-e</t>
+    <t>?TSI=Test6403bf05-4</t>
   </si>
   <si>
-    <t>?TSI=Test13ead7fe-9</t>
+    <t>?TSI=Testbe88c09e-c</t>
   </si>
   <si>
-    <t>?TSI=Test50b9ae3e-8</t>
+    <t>?TSI=Test25b592fc-a</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,36 +12,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>?TSI=Testb8285b25-2</t>
+    <t>?TSI=Test805e700b</t>
   </si>
   <si>
-    <t>?TSI=Test3c9125d2-9</t>
+    <t>4392120277</t>
   </si>
   <si>
-    <t>?TSI=Test0bdc7da3-3</t>
+    <t>?TSI=Testb039e82d</t>
   </si>
   <si>
-    <t>?TSI=Testc9bb09be-2</t>
+    <t>6392120277</t>
   </si>
   <si>
-    <t>?TSI=Test55c4bff8-6</t>
+    <t>?TSI=Test0acb1772</t>
   </si>
   <si>
-    <t>?TSI=Test8049fc90-1</t>
+    <t>9392120277</t>
   </si>
   <si>
-    <t>?TSI=Testd48f5f9d-a</t>
+    <t>?TSI=Test1ee1927f</t>
   </si>
   <si>
-    <t>?TSI=Test6403bf05-4</t>
-  </si>
-  <si>
-    <t>?TSI=Testbe88c09e-c</t>
-  </si>
-  <si>
-    <t>?TSI=Test25b592fc-a</t>
+    <t>0116620479273</t>
   </si>
 </sst>
 </file>
@@ -86,57 +80,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,30 +12,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>?TSI=Test805e700b</t>
+    <t>?TSI=Testbb4aed12</t>
   </si>
   <si>
-    <t>4392120277</t>
+    <t>2392120</t>
   </si>
   <si>
-    <t>?TSI=Testb039e82d</t>
+    <t>?TSI=Test23a51f6e</t>
   </si>
   <si>
-    <t>6392120277</t>
+    <t>83921</t>
   </si>
   <si>
-    <t>?TSI=Test0acb1772</t>
+    <t>?TSI=Test5d587460</t>
   </si>
   <si>
-    <t>9392120277</t>
+    <t>739212</t>
   </si>
   <si>
-    <t>?TSI=Test1ee1927f</t>
+    <t>?TSI=Testa57015ed</t>
   </si>
   <si>
-    <t>0116620479273</t>
+    <t>01166204</t>
+  </si>
+  <si>
+    <t>?TSI=Testd24ea860</t>
+  </si>
+  <si>
+    <t>63921</t>
   </si>
 </sst>
 </file>
@@ -80,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -115,6 +121,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,36 +12,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
-    <t>?TSI=Testbb4aed12</t>
+    <t>?TSI=Testb97f7093</t>
   </si>
   <si>
-    <t>2392120</t>
+    <t>63921</t>
   </si>
   <si>
-    <t>?TSI=Test23a51f6e</t>
+    <t>?TSI=Test18768618</t>
+  </si>
+  <si>
+    <t>?TSI=Test9781da10</t>
   </si>
   <si>
     <t>83921</t>
   </si>
   <si>
-    <t>?TSI=Test5d587460</t>
+    <t>?TSI=Test71aed6c4</t>
   </si>
   <si>
-    <t>739212</t>
+    <t>+66204</t>
   </si>
   <si>
-    <t>?TSI=Testa57015ed</t>
+    <t>?TSI=Testeebb613e</t>
   </si>
   <si>
-    <t>01166204</t>
-  </si>
-  <si>
-    <t>?TSI=Testd24ea860</t>
-  </si>
-  <si>
-    <t>63921</t>
+    <t>2392120</t>
   </si>
 </sst>
 </file>
@@ -102,31 +99,31 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,33 +12,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
-    <t>?TSI=Testb97f7093</t>
-  </si>
-  <si>
-    <t>63921</t>
-  </si>
-  <si>
-    <t>?TSI=Test18768618</t>
-  </si>
-  <si>
-    <t>?TSI=Test9781da10</t>
+    <t>?TSI=Test764914b2</t>
   </si>
   <si>
     <t>83921</t>
   </si>
   <si>
-    <t>?TSI=Test71aed6c4</t>
+    <t>?TSI=Testa87d9e09</t>
   </si>
   <si>
-    <t>+66204</t>
+    <t>739212</t>
   </si>
   <si>
-    <t>?TSI=Testeebb613e</t>
+    <t>?TSI=Test78cc7dcf</t>
   </si>
   <si>
-    <t>2392120</t>
+    <t>?TSI=Teste280c981</t>
+  </si>
+  <si>
+    <t>?TSI=Test28d1312c</t>
   </si>
 </sst>
 </file>
@@ -99,15 +93,15 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -115,15 +109,15 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,27 +12,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
-    <t>?TSI=Test764914b2</t>
+    <t>?TSI=Test09b79555</t>
   </si>
   <si>
-    <t>83921</t>
+    <t>01166204</t>
   </si>
   <si>
-    <t>?TSI=Testa87d9e09</t>
+    <t>?TSI=Test4831b865</t>
   </si>
   <si>
-    <t>739212</t>
+    <t>2392120</t>
   </si>
   <si>
-    <t>?TSI=Test78cc7dcf</t>
+    <t>?TSI=Test6ea7e70a</t>
   </si>
   <si>
-    <t>?TSI=Teste280c981</t>
+    <t>?TSI=Test425ac7f6</t>
   </si>
   <si>
-    <t>?TSI=Test28d1312c</t>
+    <t>?TSI=Testa6995fa4</t>
+  </si>
+  <si>
+    <t>3392120</t>
   </si>
 </sst>
 </file>
@@ -117,7 +120,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -12,27 +12,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
-  <si>
-    <t>?TSI=Test09b79555</t>
-  </si>
-  <si>
-    <t>01166204</t>
-  </si>
-  <si>
-    <t>?TSI=Test4831b865</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+  <si>
+    <t>?TSI=Test7d44176d</t>
+  </si>
+  <si>
+    <t>439212</t>
+  </si>
+  <si>
+    <t>?TSI=Testfc5dff19</t>
+  </si>
+  <si>
+    <t>739212</t>
+  </si>
+  <si>
+    <t>?TSI=Test236c6429</t>
+  </si>
+  <si>
+    <t>?TSI=Testf0f2a2ea</t>
   </si>
   <si>
     <t>2392120</t>
   </si>
   <si>
-    <t>?TSI=Test6ea7e70a</t>
-  </si>
-  <si>
-    <t>?TSI=Test425ac7f6</t>
-  </si>
-  <si>
-    <t>?TSI=Testa6995fa4</t>
+    <t>?TSI=Test94b9bee8</t>
+  </si>
+  <si>
+    <t>?TSI=Test5304454f</t>
+  </si>
+  <si>
+    <t>?TSI=Testc86dbe57</t>
+  </si>
+  <si>
+    <t>(222)34567</t>
+  </si>
+  <si>
+    <t>?TSI=Testdb42c3e9</t>
+  </si>
+  <si>
+    <t>?TSI=Testd6577016</t>
+  </si>
+  <si>
+    <t>abs234</t>
+  </si>
+  <si>
+    <t>?TSI=Test27b41686</t>
+  </si>
+  <si>
+    <t>?TSI=Testc93bd847</t>
+  </si>
+  <si>
+    <t>?TSI=Test80dba9b1</t>
   </si>
   <si>
     <t>3392120</t>
@@ -80,7 +110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -104,7 +134,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -112,15 +142,71 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -1,33 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\git\fs_test\src\test\resources\dataFile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461AE9A1-5620-4A06-B105-FA1CF3626C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="6000" yWindow="2640" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FIRST SHEET" r:id="rId3" sheetId="1"/>
+    <sheet name="FIRST SHEET" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Test92983d40</t>
+    <t>?TSI=Testab78dc9f</t>
   </si>
   <si>
-    <t>63921</t>
+    <t>abs234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,7 +46,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -57,15 +64,326 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -74,6 +392,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Test0a5f898f</t>
+    <t>?TSI=Test090b587a</t>
   </si>
   <si>
-    <t>(222)34567</t>
+    <t xml:space="preserve">   123</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Test090b587a</t>
+    <t>?TSI=Testb2e0f712</t>
   </si>
   <si>
-    <t xml:space="preserve">   123</t>
+    <t>539212</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -14,10 +14,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>?TSI=Testb2e0f712</t>
+    <t>?TSI=Test7878fe0b</t>
   </si>
   <si>
-    <t>539212</t>
+    <t>93921</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/dataFile/testData.xlsx
+++ b/src/test/resources/dataFile/testData.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\workspace\fs_test\src\test\resources\dataFile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5B39B6-BC3C-4B78-A529-3D2820C35F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="4755" yWindow="1485" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="FIRST_SHEET" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,8 +24,12 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,7 +340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
